--- a/public/down/Template_InputSiswa.xlsx
+++ b/public/down/Template_InputSiswa.xlsx
@@ -1,40 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Indraaaa\Documents\codingan\app-nilai\public\down\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E34BE5-2E00-4DB9-A712-1C36F9DE55F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{5615BEBA-C1D9-49E6-A268-EEAE007A5A71}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data Siswa" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
   <si>
     <t>NIS</t>
   </si>
@@ -45,6 +26,9 @@
     <t>NAMA PESERTA DIDIK</t>
   </si>
   <si>
+    <t>Kelas</t>
+  </si>
+  <si>
     <t>L/P</t>
   </si>
   <si>
@@ -63,9 +47,6 @@
     <t>ALAMAT PESERTA DIDIK</t>
   </si>
   <si>
-    <t>Kelas</t>
-  </si>
-  <si>
     <t>NAMA AYAH</t>
   </si>
   <si>
@@ -88,27 +69,129 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>1025001</t>
+  </si>
+  <si>
+    <t>0081234567</t>
+  </si>
+  <si>
+    <t>Ahmad Pratama</t>
+  </si>
+  <si>
+    <t>X RPL</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Bandung</t>
+  </si>
+  <si>
+    <t>2008-05-14</t>
+  </si>
+  <si>
+    <t>Islam</t>
+  </si>
+  <si>
+    <t>SMP Negeri 1 Bandung</t>
+  </si>
+  <si>
+    <t>Jl. Soekarno Hatta No. 12 Bandung</t>
+  </si>
+  <si>
+    <t>Budi Pratama</t>
+  </si>
+  <si>
+    <t>Siti Aminah</t>
+  </si>
+  <si>
+    <t>Wiraswasta</t>
+  </si>
+  <si>
+    <t>Ibu Rumah Tangga</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1025002</t>
+  </si>
+  <si>
+    <t>0087654321</t>
+  </si>
+  <si>
+    <t>Annisa Rahmawati</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>2008-09-22</t>
+  </si>
+  <si>
+    <t>SMP Negeri 5 Bandung</t>
+  </si>
+  <si>
+    <t>Jl. Buah Batu No. 45 Bandung</t>
+  </si>
+  <si>
+    <t>Hendra Gunawan</t>
+  </si>
+  <si>
+    <t>Dewi Lestari</t>
+  </si>
+  <si>
+    <t>Karyawan Swasta</t>
+  </si>
+  <si>
+    <t>Guru</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E293B"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F766E"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -121,52 +204,65 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF475569"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF475569"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF475569"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF475569"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFCBD5E1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FFCBD5E1"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+  <cellXfs count="8">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="49" fillId="2" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="2" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -181,44 +277,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -246,31 +342,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -298,23 +377,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -326,194 +388,227 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E4A36D-B9DF-4BD9-93A3-F11422EF4DBE}">
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="1.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="2.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.569" bestFit="true" customWidth="true" style="7"/>
+    <col min="2" max="2" width="15.139" bestFit="true" customWidth="true" style="7"/>
+    <col min="3" max="3" width="22.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="5.999" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="15.853" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="16.853" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="25.422" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="39.99" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="39.99" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="4.57" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="4.57" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="4.57" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:18" customHeight="1" ht="28">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
@@ -530,7 +625,7 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
@@ -540,7 +635,130 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:18" customHeight="1" ht="22">
+      <c r="A2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" customHeight="1" ht="22">
+      <c r="A3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>